--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9a87c600563a4478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref3f7d22d01c4908"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref3f7d22d01c4908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79b17ff87b574877"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79b17ff87b574877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc1b71a5c52624fe3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc1b71a5c52624fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3939462823794de3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3939462823794de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99013542a5fd4717"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99013542a5fd4717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7aa5a74836714543"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7aa5a74836714543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c71dd965a404038"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c71dd965a404038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R53ff4c06bf524892"/>
   </x:sheets>
 </x:workbook>
 </file>
